--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267881</v>
+        <v>125268051</v>
       </c>
       <c r="B2" t="n">
-        <v>91410</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590162</v>
+        <v>590104</v>
       </c>
       <c r="R2" t="n">
-        <v>6353482</v>
+        <v>6353459</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125268051</v>
+        <v>125267881</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,21 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590104</v>
+        <v>590162</v>
       </c>
       <c r="R3" t="n">
-        <v>6353459</v>
+        <v>6353482</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125268051</v>
+        <v>125267881</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>91410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590104</v>
+        <v>590162</v>
       </c>
       <c r="R2" t="n">
-        <v>6353459</v>
+        <v>6353482</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125267881</v>
+        <v>125268051</v>
       </c>
       <c r="B3" t="n">
-        <v>91410</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590162</v>
+        <v>590104</v>
       </c>
       <c r="R3" t="n">
-        <v>6353482</v>
+        <v>6353459</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267881</v>
+        <v>125268051</v>
       </c>
       <c r="B2" t="n">
-        <v>91410</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590162</v>
+        <v>590104</v>
       </c>
       <c r="R2" t="n">
-        <v>6353482</v>
+        <v>6353459</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125268051</v>
+        <v>125267881</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,21 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590104</v>
+        <v>590162</v>
       </c>
       <c r="R3" t="n">
-        <v>6353459</v>
+        <v>6353482</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125268051</v>
+        <v>125267881</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>91570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590104</v>
+        <v>590162</v>
       </c>
       <c r="R2" t="n">
-        <v>6353459</v>
+        <v>6353482</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125267881</v>
+        <v>125268051</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590162</v>
+        <v>590104</v>
       </c>
       <c r="R3" t="n">
-        <v>6353482</v>
+        <v>6353459</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125267881</v>
+        <v>125268051</v>
       </c>
       <c r="B2" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590162</v>
+        <v>590104</v>
       </c>
       <c r="R2" t="n">
-        <v>6353482</v>
+        <v>6353459</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125268051</v>
+        <v>125267881</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590104</v>
+        <v>590162</v>
       </c>
       <c r="R3" t="n">
-        <v>6353459</v>
+        <v>6353482</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125267881</v>
       </c>
       <c r="B3" t="n">
-        <v>91624</v>
+        <v>91631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9705-2021 artfynd.xlsx
+++ b/artfynd/A 9705-2021 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125267881</v>
       </c>
       <c r="B3" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
